--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,150 @@
       </c>
       <c r="H7" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>🎬 Citi Trivia &amp; Team Fun</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:00:41</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1865</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>71.40000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>🎬 Citi Trivia &amp; Team Fun</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:01:18</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>🏦 Banking Ops Battle</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:05:21</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1918</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>🏦 Banking Ops Battle</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:11:18</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>11689</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>65.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -699,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2418,6 +2562,1155 @@
       </c>
       <c r="K40" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>🐸</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1865</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ChillKarthik</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>🐨</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>🦄</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1520</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>🦉</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1510</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>🐼</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1365</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>🐯</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>7</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>🦊</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>🦄</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>🐸</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Octo-Ops</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>🐙</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>🦉</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>🐯</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>🦁</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>🦊</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>🦁</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1918</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Octo-Ops</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>🐙</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1718</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>🦉</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1686</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>🐼</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1486</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>🐸</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ChillKarthik</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>🐨</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>🦉</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>11689</v>
+      </c>
+      <c r="G61" t="n">
+        <v>7</v>
+      </c>
+      <c r="H61" t="n">
+        <v>10</v>
+      </c>
+      <c r="I61" t="n">
+        <v>5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>🦄</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>11258</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>🐸</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>11234</v>
+      </c>
+      <c r="G63" t="n">
+        <v>7</v>
+      </c>
+      <c r="H63" t="n">
+        <v>10</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>🦁</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>10687</v>
+      </c>
+      <c r="G64" t="n">
+        <v>7</v>
+      </c>
+      <c r="H64" t="n">
+        <v>10</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Red Arcs</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>🐼</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>9816</v>
+      </c>
+      <c r="G65" t="n">
+        <v>6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" t="n">
+        <v>6</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Blue Sparks</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>🐯</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>6825</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" t="n">
+        <v>10</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>7</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>🐼</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>3228</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +3724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8670,6 +9963,3562 @@
         <v>0</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>In which year was Citi (then City Bank of New York) founded?</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ChillKarthik</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>In which year was Citi (then City Bank of New York) founded?</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>In which year was Citi (then City Bank of New York) founded?</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>In which year was Citi (then City Bank of New York) founded?</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>In which year was Citi (then City Bank of New York) founded?</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>In which year was Citi (then City Bank of New York) founded?</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>056ab5a6a2</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>QuizNinja</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>In which year was Citi (then City Bank of New York) founded?</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>(no answer)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>20</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>In which year was Citi (then City Bank of New York) founded?</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>fa2bd021a8</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>In which year was Citi (then City Bank of New York) founded?</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>9</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Octo-Ops</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Offer compensation straight away</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>26127a4e81</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ChillKarthik</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Explain why the transfers happened</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G165" t="b">
+        <v>1</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>What does TKT stand for?</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Empathy Statement</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="G166" t="b">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>3</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of workforce management?</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="G167" t="b">
+        <v>1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>3</v>
+      </c>
+      <c r="J167" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>4</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of empathy statements?</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>The metric dashboard turns green regardless of performance</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="G168" t="b">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>5</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “routing an issue to higher expertise or authority”?</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="G169" t="b">
+        <v>1</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>6</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Your queue is on fire: 40 calls waiting, 5 agents. What do you do in the next 10 minutes?</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Use the IVR data and CRM history so the customer never repeats themselves, then solve it on first contact.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>(subjective — scored by votes)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" t="n">
+        <v>45</v>
+      </c>
+      <c r="J170" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>7</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “share of customers successfully kept over a period”?</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="G171" t="b">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>8</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “scripted behaviour proven to lift customer satisfaction”?</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="G172" t="b">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>9</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>What does WFO stand for?</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="G173" t="b">
+        <v>1</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>NightOwl_Sam</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>10</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>What does CLF stand for?</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="G174" t="b">
+        <v>1</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G175" t="b">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>What does TKT stand for?</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="G176" t="b">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>3</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of workforce management?</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="G177" t="b">
+        <v>1</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>4</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of empathy statements?</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="G178" t="b">
+        <v>1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>5</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “routing an issue to higher expertise or authority”?</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="G179" t="b">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>6</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Your queue is on fire: 40 calls waiting, 5 agents. What do you do in the next 10 minutes?</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>I'd pull the agent-assist summary, confirm the intent, and give one clear next step instead of transferring the call.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>(subjective — scored by votes)</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>7</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “share of customers successfully kept over a period”?</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>FLR (First Line Resolution)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="G181" t="b">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>8</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “scripted behaviour proven to lift customer satisfaction”?</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="G182" t="b">
+        <v>1</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J182" t="n">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>9</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>What does WFO stand for?</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="G183" t="b">
+        <v>1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J183" t="n">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Sneha ✨</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>10</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>What does CLF stand for?</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="G184" t="b">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G185" t="b">
+        <v>1</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>What does TKT stand for?</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Empathy Statement</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="G186" t="b">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of workforce management?</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="G187" t="b">
+        <v>1</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>4</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of empathy statements?</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="G188" t="b">
+        <v>1</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>5</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “routing an issue to higher expertise or authority”?</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="G189" t="b">
+        <v>1</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>6</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Your queue is on fire: 40 calls waiting, 5 agents. What do you do in the next 10 minutes?</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>I would first acknowledge the customer's frustration, then verify the account and resolve the root cause before offering a goodwill gesture.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>(subjective — scored by votes)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>7</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “share of customers successfully kept over a period”?</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="G191" t="b">
+        <v>1</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>12</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>8</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “scripted behaviour proven to lift customer satisfaction”?</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>SOFT (Soft Skills)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="G192" t="b">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>9</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>What does WFO stand for?</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="G193" t="b">
+        <v>1</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>KermitTheDev</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>10</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>What does CLF stand for?</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="G194" t="b">
+        <v>1</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G195" t="b">
+        <v>1</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>What does TKT stand for?</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="G196" t="b">
+        <v>1</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>3</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of workforce management?</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="G197" t="b">
+        <v>1</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+      <c r="I197" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>4</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of empathy statements?</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>The metric dashboard turns green regardless of performance</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="G198" t="b">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>5</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “routing an issue to higher expertise or authority”?</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>HOLD (Hold Time)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="G199" t="b">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>6</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Your queue is on fire: 40 calls waiting, 5 agents. What do you do in the next 10 minutes?</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Root-cause it: one fixed process beats a hundred apologies.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>(subjective — scored by votes)</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>7</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “share of customers successfully kept over a period”?</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="G201" t="b">
+        <v>1</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>7</v>
+      </c>
+      <c r="J201" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>8</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “scripted behaviour proven to lift customer satisfaction”?</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="G202" t="b">
+        <v>1</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>9</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>What does WFO stand for?</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="G203" t="b">
+        <v>1</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Arjun_Roars</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>10</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>What does CLF stand for?</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="G204" t="b">
+        <v>1</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G205" t="b">
+        <v>1</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>What does TKT stand for?</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="G206" t="b">
+        <v>1</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+      <c r="I206" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>3</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of workforce management?</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="G207" t="b">
+        <v>1</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J207" t="n">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>4</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of empathy statements?</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="G208" t="b">
+        <v>1</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>5</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “routing an issue to higher expertise or authority”?</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="G209" t="b">
+        <v>1</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>6</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Your queue is on fire: 40 calls waiting, 5 agents. What do you do in the next 10 minutes?</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Listen fully, apologise once sincerely, fix the issue, and follow up within 24 hours so the customer never has to call back.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>(subjective — scored by votes)</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>45</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>7</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “share of customers successfully kept over a period”?</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="G211" t="b">
+        <v>1</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>8</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “scripted behaviour proven to lift customer satisfaction”?</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>WFO (Workforce Optimisation)</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="G212" t="b">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>9</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>What does WFO stand for?</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Retention Rate</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="G213" t="b">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Priya P.</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>10</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>What does CLF stand for?</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Positive Key Behaviour</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="G214" t="b">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Explain why the transfers happened</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G215" t="b">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>What does TKT stand for?</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="G216" t="b">
+        <v>1</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>3</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of workforce management?</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="G217" t="b">
+        <v>1</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>4</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of empathy statements?</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>The metric dashboard turns green regardless of performance</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="G218" t="b">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>5</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “routing an issue to higher expertise or authority”?</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="G219" t="b">
+        <v>1</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>6</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Your queue is on fire: 40 calls waiting, 5 agents. What do you do in the next 10 minutes?</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Turn the complaint into feedback — log it, fix it, and tell the customer what changed because of them.</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>(subjective — scored by votes)</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>7</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “share of customers successfully kept over a period”?</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="G221" t="b">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>8</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “scripted behaviour proven to lift customer satisfaction”?</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>CBAK (Callback)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="G222" t="b">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>9</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>What does WFO stand for?</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>First Line Resolution</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="G223" t="b">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>TigerTeam_Vik</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>10</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>What does CLF stand for?</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Voice of the Customer</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="G224" t="b">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>A customer calls angry after being transferred three times. What should the agent do FIRST?</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Transfer to a supervisor immediately</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Acknowledge the frustration and own the issue</t>
+        </is>
+      </c>
+      <c r="G225" t="b">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>2</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>What does TKT stand for?</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="G226" t="b">
+        <v>1</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J226" t="n">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>3</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of workforce management?</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>The right number of agents are staffed for forecast volume</t>
+        </is>
+      </c>
+      <c r="G227" t="b">
+        <v>1</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>10</v>
+      </c>
+      <c r="J227" t="n">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>4</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Which of the following is a genuine benefit of empathy statements?</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>(no answer)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Customers feel heard before the fix begins</t>
+        </is>
+      </c>
+      <c r="G228" t="b">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>20</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>5</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “routing an issue to higher expertise or authority”?</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>SRQ (Service Request)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>ESC (Escalation)</t>
+        </is>
+      </c>
+      <c r="G229" t="b">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>6</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Your queue is on fire: 40 calls waiting, 5 agents. What do you do in the next 10 minutes?</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>KJSNDBCNSDKJCNSDCNSD</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>(subjective — scored by votes)</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>7</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “share of customers successfully kept over a period”?</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>(no answer)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>RET (Retention Rate)</t>
+        </is>
+      </c>
+      <c r="G231" t="b">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" t="n">
+        <v>20</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>8</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Which term matches this definition: “scripted behaviour proven to lift customer satisfaction”?</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>(no answer)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>PKB (Positive Key Behaviour)</t>
+        </is>
+      </c>
+      <c r="G232" t="b">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="n">
+        <v>20</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>9</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>What does WFO stand for?</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>(no answer)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Workforce Optimisation</t>
+        </is>
+      </c>
+      <c r="G233" t="b">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" t="n">
+        <v>20</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>c6493184c3</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>10</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>What does CLF stand for?</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>(no answer)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Closed Loop Feedback</t>
+        </is>
+      </c>
+      <c r="G234" t="b">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" t="n">
+        <v>20</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
